--- a/AAII_Financials/Quarterly/OBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
   <si>
     <t>OBT</t>
   </si>
@@ -656,119 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -781,83 +782,86 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E8" s="3">
         <v>32500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>30300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>27800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>26900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>24900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>25600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13600</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,8 +874,11 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -959,53 +966,56 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E10" s="3">
         <v>32500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>29900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>27800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>27400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1048,8 +1058,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1081,8 +1094,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1170,8 +1184,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,8 +1276,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1303,8 +1323,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1348,8 +1368,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1360,10 +1383,10 @@
         <v>500</v>
       </c>
       <c r="F15" s="3">
+        <v>500</v>
+      </c>
+      <c r="G15" s="3">
         <v>400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>500</v>
       </c>
       <c r="H15" s="3">
         <v>500</v>
@@ -1390,10 +1413,10 @@
         <v>500</v>
       </c>
       <c r="P15" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q15" s="3">
         <v>600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>-100</v>
       </c>
       <c r="R15" s="3">
         <v>-100</v>
@@ -1422,8 +1445,8 @@
       <c r="Z15" s="3">
         <v>-100</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
+      <c r="AA15" s="3">
+        <v>-100</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
@@ -1437,8 +1460,11 @@
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1467,83 +1493,84 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>16400</v>
       </c>
       <c r="G17" s="3">
         <v>16400</v>
       </c>
       <c r="H17" s="3">
+        <v>16400</v>
+      </c>
+      <c r="I17" s="3">
         <v>16100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2400</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1556,83 +1583,86 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E18" s="3">
         <v>15000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>14100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,8 +1675,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1678,13 +1711,14 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>400</v>
@@ -1702,13 +1736,13 @@
         <v>400</v>
       </c>
       <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>500</v>
       </c>
       <c r="M20" s="3">
         <v>500</v>
@@ -1717,44 +1751,44 @@
         <v>500</v>
       </c>
       <c r="O20" s="3">
+        <v>500</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7600</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1767,77 +1801,80 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E21" s="3">
         <v>15100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1856,8 +1893,11 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1900,8 +1940,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1945,83 +1985,86 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E23" s="3">
         <v>14600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3600</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2034,83 +2077,86 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,8 +2169,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2212,83 +2261,86 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E26" s="3">
         <v>11300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2900</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2301,83 +2353,86 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E27" s="3">
         <v>11300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2900</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2390,8 +2445,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2479,8 +2537,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2568,8 +2629,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2657,8 +2721,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2746,13 +2813,16 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>-400</v>
@@ -2770,13 +2840,13 @@
         <v>-400</v>
       </c>
       <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-500</v>
       </c>
       <c r="M32" s="3">
         <v>-500</v>
@@ -2785,44 +2855,44 @@
         <v>-500</v>
       </c>
       <c r="O32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7600</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,83 +2905,86 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E33" s="3">
         <v>11300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2900</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,8 +2997,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3013,83 +3089,86 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E35" s="3">
         <v>11300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2900</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3102,88 +3181,91 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3278,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3229,8 +3314,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3262,77 +3348,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>334900</v>
+      </c>
+      <c r="E41" s="3">
         <v>257500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>204200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>189900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>175600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>164200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>150300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>160900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>189700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>147400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>158700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>178600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>165300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>180200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>271400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>356300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>306200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>390100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>322900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>253100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3438,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3440,8 +3530,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3484,8 +3577,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3529,8 +3622,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3573,8 +3669,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3618,53 +3714,56 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E45" s="3">
         <v>11000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>10500</v>
       </c>
       <c r="G45" s="3">
         <v>10500</v>
       </c>
       <c r="H45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I45" s="3">
         <v>11000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3707,53 +3806,56 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>409300</v>
+      </c>
+      <c r="E46" s="3">
         <v>268500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>214600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>186100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>175200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>157000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>170900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>199300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>154900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>153300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>165000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>184400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>171300</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3796,53 +3898,56 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>395900</v>
+      </c>
+      <c r="E47" s="3">
         <v>407500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>419400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>426600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>410800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>443800</v>
       </c>
       <c r="I47" s="3">
         <v>443800</v>
       </c>
       <c r="J47" s="3">
+        <v>443800</v>
+      </c>
+      <c r="K47" s="3">
         <v>469500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>463100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>476100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>489900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>478700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>503200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>526300</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -3885,77 +3990,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E48" s="3">
         <v>15600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>14300</v>
       </c>
       <c r="T48" s="3">
         <v>14300</v>
       </c>
       <c r="U48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="V48" s="3">
         <v>14600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3974,8 +4082,11 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3983,68 +4094,68 @@
         <v>5800</v>
       </c>
       <c r="E49" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F49" s="3">
         <v>5900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>6000</v>
       </c>
       <c r="G49" s="3">
         <v>6000</v>
       </c>
       <c r="H49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I49" s="3">
         <v>6100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>6300</v>
       </c>
       <c r="K49" s="3">
         <v>6300</v>
       </c>
       <c r="L49" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M49" s="3">
         <v>6400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6500</v>
       </c>
       <c r="N49" s="3">
         <v>6500</v>
       </c>
       <c r="O49" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P49" s="3">
         <v>6600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6700</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>6800</v>
       </c>
       <c r="R49" s="3">
         <v>6800</v>
       </c>
       <c r="S49" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T49" s="3">
         <v>6900</v>
-      </c>
-      <c r="T49" s="3">
-        <v>7000</v>
       </c>
       <c r="U49" s="3">
         <v>7000</v>
       </c>
       <c r="V49" s="3">
+        <v>7000</v>
+      </c>
+      <c r="W49" s="3">
         <v>7100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4063,8 +4174,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4152,8 +4266,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4241,53 +4358,56 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E52" s="3">
         <v>84000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>59400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>81900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>99000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>91300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>70100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>93100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>90700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>92100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>75600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>99000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>95000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>95500</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -4330,8 +4450,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4419,77 +4542,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2800400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2705600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2659400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2636500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2606300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2560100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2509900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2519100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2481200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2452500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2485500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2447300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2493900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2455000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2287300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2368400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2392000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2281100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2142600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2175200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2052200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1908800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4508,8 +4634,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4541,8 +4670,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4574,53 +4704,54 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2431200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2349700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2310400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2278900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2276700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2281700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2153400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2140000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2199300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2149400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2038700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2105000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2138200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2025800</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -4663,8 +4794,11 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4672,44 +4806,44 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>113500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>132000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>50000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>28000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>224500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>146000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>156500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>229000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4752,8 +4886,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4796,33 +4933,33 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>23900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>22200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>20500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>20400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>23000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>20300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>17800</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4841,53 +4978,56 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2459100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2379400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2331100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2331800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2324000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2329200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2284300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2296400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2274100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2204300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2279900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2273900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2316300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2277000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4930,8 +5070,11 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4939,34 +5082,34 @@
         <v>34600</v>
       </c>
       <c r="E61" s="3">
+        <v>34600</v>
+      </c>
+      <c r="F61" s="3">
         <v>38000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34500</v>
-      </c>
-      <c r="G61" s="3">
-        <v>29600</v>
       </c>
       <c r="H61" s="3">
         <v>29600</v>
       </c>
       <c r="I61" s="3">
+        <v>29600</v>
+      </c>
+      <c r="J61" s="3">
         <v>33300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>29600</v>
       </c>
       <c r="K61" s="3">
         <v>29600</v>
       </c>
       <c r="L61" s="3">
+        <v>29600</v>
+      </c>
+      <c r="M61" s="3">
         <v>79500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>32700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>29500</v>
       </c>
       <c r="O61" s="3">
         <v>29500</v>
@@ -4975,10 +5118,10 @@
         <v>29500</v>
       </c>
       <c r="Q61" s="3">
+        <v>29500</v>
+      </c>
+      <c r="R61" s="3">
         <v>19400</v>
-      </c>
-      <c r="R61" s="3">
-        <v>22400</v>
       </c>
       <c r="S61" s="3">
         <v>22400</v>
@@ -4996,11 +5139,11 @@
         <v>22400</v>
       </c>
       <c r="X61" s="3">
+        <v>22400</v>
+      </c>
+      <c r="Y61" s="3">
         <v>22300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5019,52 +5162,55 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>5100</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>5800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>6300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -5108,8 +5254,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5197,8 +5346,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5286,8 +5438,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5375,77 +5530,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2493700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2414000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2375000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2366300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2353700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2358800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2324400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2326000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2303600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2283800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2320100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2303400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2345700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2306400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2149200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2232200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2246300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2116500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1959700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1994600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1911300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1773700</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5464,8 +5622,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5497,8 +5658,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5586,8 +5748,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5675,8 +5840,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5764,8 +5932,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5853,77 +6024,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>184600</v>
+      </c>
+      <c r="E72" s="3">
         <v>173300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>164400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>154400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>146100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>137100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>129900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>124200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>122300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>115400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>107400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>100500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>92800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>85000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>84600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>76900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>70100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>64900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>60600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>56100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>51800</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5942,8 +6116,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6031,8 +6208,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6120,8 +6300,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6209,77 +6392,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>306600</v>
+      </c>
+      <c r="E76" s="3">
         <v>291700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>284400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>270100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>252600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>201300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>185500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>193100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>177500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>168700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>165400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>143900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>148200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>148600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>138100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>136200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>145700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>164500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>182800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>180600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>140900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>135100</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6298,8 +6484,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6387,88 +6576,91 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6481,83 +6673,86 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E81" s="3">
         <v>11300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2900</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6765,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6603,8 +6801,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6612,10 +6811,10 @@
         <v>400</v>
       </c>
       <c r="E83" s="3">
+        <v>400</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
@@ -6633,13 +6832,13 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
+        <v>400</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -6648,13 +6847,13 @@
         <v>400</v>
       </c>
       <c r="Q83" s="3">
+        <v>400</v>
+      </c>
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>400</v>
       </c>
       <c r="T83" s="3">
         <v>400</v>
@@ -6671,8 +6870,8 @@
       <c r="X83" s="3">
         <v>400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>400</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -6692,8 +6891,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6781,8 +6983,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6870,8 +7075,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6959,8 +7167,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7048,8 +7259,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7137,77 +7351,80 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E89" s="3">
         <v>10200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7226,8 +7443,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7259,76 +7479,77 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-600</v>
       </c>
       <c r="V91" s="3">
         <v>-600</v>
       </c>
       <c r="W91" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>-400</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -7348,8 +7569,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7437,8 +7661,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7526,77 +7753,80 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E94" s="3">
         <v>6100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>32500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-38200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-86300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-220900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-111000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-51000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-72100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-113700</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7615,8 +7845,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7648,8 +7881,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7660,19 +7894,19 @@
         <v>2400</v>
       </c>
       <c r="F96" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G96" s="3">
         <v>1700</v>
-      </c>
-      <c r="G96" s="3">
-        <v>1500</v>
       </c>
       <c r="H96" s="3">
         <v>1500</v>
       </c>
       <c r="I96" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J96" s="3">
         <v>1400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>1300</v>
       </c>
       <c r="K96" s="3">
         <v>1300</v>
@@ -7693,10 +7927,10 @@
         <v>1300</v>
       </c>
       <c r="Q96" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-1100</v>
       </c>
       <c r="S96" s="3">
         <v>-1100</v>
@@ -7711,13 +7945,13 @@
         <v>-1100</v>
       </c>
       <c r="W96" s="3">
-        <v>-900</v>
+        <v>-1100</v>
       </c>
       <c r="X96" s="3">
         <v>-900</v>
       </c>
       <c r="Y96" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="Z96" s="3">
         <v>0</v>
@@ -7737,8 +7971,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7826,8 +8063,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7915,8 +8155,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8004,77 +8247,80 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E100" s="3">
         <v>36900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>37700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>33700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>21200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>20500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-37400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>10900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>38600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>157400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-86000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>128600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>158000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-38600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>114300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>137100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>243100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8093,8 +8339,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8137,8 +8386,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8182,77 +8431,80 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E102" s="3">
         <v>53300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>45000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>79200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-94200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-91200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-84900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>50100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-83900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>67200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>69800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>131900</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8269,6 +8521,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
